--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008450004899078973</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>20756369</v>
+        <v>4180796</v>
       </c>
       <c r="L2" t="n">
-        <v>7842835</v>
+        <v>1540495</v>
       </c>
       <c r="M2" t="n">
-        <v>1435673</v>
+        <v>290227</v>
       </c>
       <c r="N2" t="n">
-        <v>31901</v>
+        <v>6291</v>
       </c>
       <c r="O2" t="n">
-        <v>871172</v>
+        <v>172251</v>
       </c>
       <c r="P2" t="n">
-        <v>17646</v>
+        <v>2827</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999042749404907</v>
+        <v>0.9999333024024963</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7178440093994141</v>
+        <v>0.7133005857467651</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5342109799385071</v>
+        <v>0.5377152562141418</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4014006853103638</v>
+        <v>0.4029626548290253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04511692002415657</v>
+        <v>0.04523848742246628</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4030587673187256</v>
+        <v>0.4057404100894928</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4533682763576508</v>
+        <v>0.4500159323215485</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026420486158906</v>
       </c>
       <c r="C3" t="n">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="D3" t="n">
-        <v>20756369</v>
+        <v>4180796</v>
       </c>
       <c r="E3" t="n">
-        <v>4168525</v>
+        <v>795136</v>
       </c>
       <c r="F3" t="n">
-        <v>179998</v>
+        <v>34975</v>
       </c>
       <c r="G3" t="n">
-        <v>20093</v>
+        <v>3750</v>
       </c>
       <c r="H3" t="n">
-        <v>16509</v>
+        <v>2726</v>
       </c>
       <c r="I3" t="n">
-        <v>757</v>
+        <v>118</v>
       </c>
       <c r="J3" t="n">
-        <v>50080088</v>
+        <v>10016201</v>
       </c>
       <c r="K3" t="n">
-        <v>48346954</v>
+        <v>9631625</v>
       </c>
       <c r="L3" t="n">
-        <v>58488502</v>
+        <v>11731778</v>
       </c>
       <c r="M3" t="n">
-        <v>74845719</v>
+        <v>14966175</v>
       </c>
       <c r="N3" t="n">
-        <v>80527180</v>
+        <v>16107570</v>
       </c>
       <c r="O3" t="n">
-        <v>77811904</v>
+        <v>15567764</v>
       </c>
       <c r="P3" t="n">
-        <v>80660139</v>
+        <v>16132752</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8255478143692017</v>
+        <v>0.83323073387146</v>
       </c>
       <c r="S3" t="n">
-        <v>0.480531245470047</v>
+        <v>0.4706061780452728</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3079986870288849</v>
+        <v>0.3109289705753326</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07158356159925461</v>
+        <v>0.070481076836586</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3421908318996429</v>
+        <v>0.3380440175533295</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01825602538883686</v>
+        <v>0.01461790222674608</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03197089671244802</v>
       </c>
       <c r="C4" t="n">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>7246735</v>
+        <v>1491010</v>
       </c>
       <c r="E4" t="n">
-        <v>7842835</v>
+        <v>1540495</v>
       </c>
       <c r="F4" t="n">
-        <v>955980</v>
+        <v>189714</v>
       </c>
       <c r="G4" t="n">
-        <v>109144</v>
+        <v>21003</v>
       </c>
       <c r="H4" t="n">
-        <v>163393</v>
+        <v>30711</v>
       </c>
       <c r="I4" t="n">
-        <v>2963</v>
+        <v>466</v>
       </c>
       <c r="J4" t="n">
-        <v>3022</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>8158506</v>
+        <v>1680402</v>
       </c>
       <c r="L4" t="n">
-        <v>6838322</v>
+        <v>1324395</v>
       </c>
       <c r="M4" t="n">
-        <v>2140985</v>
+        <v>430006</v>
       </c>
       <c r="N4" t="n">
-        <v>675173</v>
+        <v>132772</v>
       </c>
       <c r="O4" t="n">
-        <v>1290230</v>
+        <v>252284</v>
       </c>
       <c r="P4" t="n">
-        <v>21276</v>
+        <v>3455</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999521374702454</v>
+        <v>0.9999666810035706</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7679378986358643</v>
+        <v>0.7686154842376709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5059512853622437</v>
+        <v>0.5019274950027466</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3485508859157562</v>
+        <v>0.3510133922100067</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05534903705120087</v>
+        <v>0.05510662496089935</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3701391220092773</v>
+        <v>0.3688114881515503</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03509871289134026</v>
+        <v>0.02831601351499557</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>386</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>674397</v>
+        <v>140165</v>
       </c>
       <c r="E5" t="n">
-        <v>1977404</v>
+        <v>391560</v>
       </c>
       <c r="F5" t="n">
-        <v>1435673</v>
+        <v>290227</v>
       </c>
       <c r="G5" t="n">
-        <v>174968</v>
+        <v>34613</v>
       </c>
       <c r="H5" t="n">
-        <v>393329</v>
+        <v>75933</v>
       </c>
       <c r="I5" t="n">
-        <v>5139</v>
+        <v>865</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4386171</v>
+        <v>836777</v>
       </c>
       <c r="L5" t="n">
-        <v>8478341</v>
+        <v>1732932</v>
       </c>
       <c r="M5" t="n">
-        <v>3225623</v>
+        <v>643192</v>
       </c>
       <c r="N5" t="n">
-        <v>413746</v>
+        <v>82967</v>
       </c>
       <c r="O5" t="n">
-        <v>1674694</v>
+        <v>337301</v>
       </c>
       <c r="P5" t="n">
-        <v>948939</v>
+        <v>190566</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999629855155945</v>
+        <v>0.9999741911888123</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8463565707206726</v>
+        <v>0.8458517789840698</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8124061226844788</v>
+        <v>0.8127739429473877</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9342713952064514</v>
+        <v>0.9342789649963379</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9866632223129272</v>
+        <v>0.9867884516716003</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9636865258216858</v>
+        <v>0.9638947248458862</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881170988082886</v>
+        <v>0.9881184697151184</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>233</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>120502</v>
+        <v>24974</v>
       </c>
       <c r="E6" t="n">
-        <v>130713</v>
+        <v>25617</v>
       </c>
       <c r="F6" t="n">
-        <v>119613</v>
+        <v>24115</v>
       </c>
       <c r="G6" t="n">
-        <v>31901</v>
+        <v>6291</v>
       </c>
       <c r="H6" t="n">
-        <v>41455</v>
+        <v>8018</v>
       </c>
       <c r="I6" t="n">
-        <v>1230</v>
+        <v>206</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>910</v>
+        <v>108</v>
       </c>
       <c r="D7" t="n">
-        <v>106841</v>
+        <v>22106</v>
       </c>
       <c r="E7" t="n">
-        <v>499735</v>
+        <v>99481</v>
       </c>
       <c r="F7" t="n">
-        <v>756451</v>
+        <v>154810</v>
       </c>
       <c r="G7" t="n">
-        <v>299570</v>
+        <v>58996</v>
       </c>
       <c r="H7" t="n">
-        <v>871172</v>
+        <v>172251</v>
       </c>
       <c r="I7" t="n">
-        <v>11187</v>
+        <v>1800</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1078</v>
+        <v>120</v>
       </c>
       <c r="D8" t="n">
-        <v>10031</v>
+        <v>2147</v>
       </c>
       <c r="E8" t="n">
-        <v>61945</v>
+        <v>12601</v>
       </c>
       <c r="F8" t="n">
-        <v>128943</v>
+        <v>26392</v>
       </c>
       <c r="G8" t="n">
-        <v>71398</v>
+        <v>14410</v>
       </c>
       <c r="H8" t="n">
-        <v>675544</v>
+        <v>134896</v>
       </c>
       <c r="I8" t="n">
-        <v>17646</v>
+        <v>2827</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
